--- a/artfynd/A 20993-2026 artfynd.xlsx
+++ b/artfynd/A 20993-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127610169</v>
       </c>
       <c r="B2" t="n">
-        <v>96595</v>
+        <v>97231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127610166</v>
+        <v>127610167</v>
       </c>
       <c r="B3" t="n">
-        <v>80168</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -872,7 +872,7 @@
         <v>127610164</v>
       </c>
       <c r="B4" t="n">
-        <v>80161</v>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127610167</v>
+        <v>127610165</v>
       </c>
       <c r="B5" t="n">
-        <v>80132</v>
+        <v>80467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127610165</v>
+        <v>127610166</v>
       </c>
       <c r="B6" t="n">
-        <v>80167</v>
+        <v>80468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/artfynd/A 20993-2026 artfynd.xlsx
+++ b/artfynd/A 20993-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127610169</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127610167</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127610164</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127610165</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,8 +1182,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127610166</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>